--- a/data/level3_analysis.xlsx
+++ b/data/level3_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>bot1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>test111</t>
         </is>
       </c>
       <c r="C2" t="b">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample</t>
+          <t>no realtime audio sample</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>bot1</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -486,119 +486,99 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample</t>
+          <t>no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>m0</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>m0</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>test666</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>no fonts detected</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>test666</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>no fonts detected</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>bot02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>bot1</t>
         </is>
       </c>
       <c r="C9" t="b">
@@ -606,47 +586,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no fonts detected; TouchEvent not supported</t>
+          <t>no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="b">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="b">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>no fonts detected; TouchEvent not supported</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
@@ -658,7 +630,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>bot02</t>
         </is>
       </c>
       <c r="C12" t="b">
@@ -666,14 +638,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>bot02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -682,7 +654,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>no fonts detected; suspicious WebGL (Google Inc. (Google), ANGLE (Google, Vulkan 1.3.0 (SwiftShader Device (Subzero) (0x0000C0DE)), SwiftShader driver))</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
@@ -694,7 +666,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>bot02</t>
         </is>
       </c>
       <c r="C14" t="b">
@@ -702,19 +674,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>no fonts detected; suspicious WebGL (Google Inc. (Google), ANGLE (Google, Vulkan 1.3.0 (SwiftShader Device (Subzero) (0x0000C0DE)), SwiftShader driver))</t>
+          <t>timezone info abnormal; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>bot03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>m0</t>
+          <t>bottest01</t>
         </is>
       </c>
       <c r="C15" t="b">
@@ -722,19 +694,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample</t>
+          <t>no fonts detected; no offline audio sample; no realtime audio sample</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>guest</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>bot03</t>
         </is>
       </c>
       <c r="C16" t="b">
@@ -742,467 +714,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C17" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C18" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C19" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C20" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>no fonts detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>no fonts detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>test666</t>
-        </is>
-      </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>no fonts detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C23" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>no fonts detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
-      <c r="C25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
-      <c r="C28" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
-      <c r="C29" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C30" t="b">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C31" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>no fonts detected; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C32" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C34" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>no fonts detected; no realtime audio sample; TouchEvent not supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>very few fonts (1); no realtime audio sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>very few fonts (1); no realtime audio sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C38" t="b">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>very few fonts (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C39" t="b">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>very few fonts (1)</t>
+          <t>no realtime audio sample</t>
         </is>
       </c>
     </row>

--- a/data/level3_analysis.xlsx
+++ b/data/level3_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,7 @@
           <t>bot1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>test111</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="b">
         <v>1</v>
       </c>
@@ -476,11 +472,7 @@
           <t>guest</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>bot1</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="b">
         <v>1</v>
       </c>
@@ -576,11 +568,7 @@
           <t>bot02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>bot1</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="b">
         <v>1</v>
       </c>
@@ -628,11 +616,7 @@
           <t>guest</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>bot02</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="b">
         <v>1</v>
       </c>
@@ -664,11 +648,7 @@
           <t>guest</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>bot02</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="b">
         <v>1</v>
       </c>
@@ -684,11 +664,7 @@
           <t>bot03</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>bottest01</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="b">
         <v>1</v>
       </c>
@@ -704,17 +680,1821 @@
           <t>guest</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>no realtime audio sample; TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>no realtime audio sample; TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bot06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>speech synthesis missing; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>speech synthesis missing; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>bot03</t>
         </is>
       </c>
-      <c r="C16" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bot08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bot08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="b">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bot04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bot04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bot04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="b">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="b">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>bot04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bot04</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>bot04</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="b">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="b">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>bot08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="b">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="b">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>bot08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="b">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="b">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="b">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="b">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="b">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="b">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="b">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="b">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="b">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>no realtime audio sample; TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="b">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>no realtime audio sample; TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="b">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="b">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="b">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="b">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="b">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="b">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="b">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="b">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="b">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="b">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="b">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="b">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="b">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="b">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="b">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="b">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="b">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="b">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="b">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="b">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="b">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="b">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="b">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>bot05</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="b">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="b">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>m.ik.k.am.u.e.rtio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="b">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>m.ik.k.am.u.e.rtio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="b">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="b">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="b">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="b">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>no realtime audio sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="b">
+        <v>0</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>

--- a/data/level3_analysis.xlsx
+++ b/data/level3_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,10 +441,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>is_bot</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>reasons</t>
         </is>
@@ -457,12 +462,17 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-09-13T12:25:40</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -473,12 +483,17 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-09-13T12:25:42</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -489,12 +504,17 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:23:37</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -505,12 +525,17 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:24:09</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -521,12 +546,17 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:24:14</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -537,12 +567,17 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:24:23</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -553,12 +588,17 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:24:25</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -569,12 +609,17 @@
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:37:24</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -585,12 +630,17 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:40:59</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -601,12 +651,17 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:42:38</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -617,12 +672,17 @@
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:42:41</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -633,12 +693,17 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:43:43</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -649,12 +714,17 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:43:46</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -665,12 +735,17 @@
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>no fonts detected; no offline audio sample; no realtime audio sample</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:54:44</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no fonts detected; no offline audio sample</t>
         </is>
       </c>
     </row>
@@ -681,12 +756,17 @@
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-09-13T13:54:52</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -697,12 +777,17 @@
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-09-15T11:58:03</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
         </is>
       </c>
     </row>
@@ -713,12 +798,17 @@
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-09-15T11:58:18</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
         </is>
       </c>
     </row>
@@ -729,12 +819,17 @@
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-09-15T13:03:46</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -745,12 +840,17 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-09-15T14:03:26</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
         </is>
       </c>
     </row>
@@ -761,12 +861,17 @@
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-09-15T17:11:02</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -777,12 +882,17 @@
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-09-15T17:11:05</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -793,12 +903,17 @@
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>no realtime audio sample; TouchEvent not supported</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-09-15T17:11:45</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
         </is>
       </c>
     </row>
@@ -809,12 +924,17 @@
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>no realtime audio sample; TouchEvent not supported</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-09-15T17:11:47</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
         </is>
       </c>
     </row>
@@ -825,12 +945,17 @@
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-09-16T13:25:10</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
         </is>
       </c>
     </row>
@@ -841,12 +966,17 @@
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>speech synthesis missing; no realtime audio sample</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-09-16T15:41:16</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
         </is>
       </c>
     </row>
@@ -857,12 +987,17 @@
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>speech synthesis missing; no realtime audio sample</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-09-16T15:41:22</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
         </is>
       </c>
     </row>
@@ -873,12 +1008,17 @@
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-09-17T06:57:11</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -889,12 +1029,17 @@
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-09-17T06:57:11</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -905,12 +1050,17 @@
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="b">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-09-17T06:57:14</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -921,12 +1071,17 @@
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-09-17T07:04:37</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -937,12 +1092,17 @@
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025-09-17T07:04:39</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -953,12 +1113,17 @@
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-09-18T08:13:30</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -969,12 +1134,17 @@
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2025-09-18T08:13:30</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -985,12 +1155,17 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-09-18T08:13:33</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1176,17 @@
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="b">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-09-18T08:13:34</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1197,17 @@
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-09-18T08:13:34</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1218,17 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="b">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:42:01</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1239,17 @@
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="b">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:42:04</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1260,17 @@
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="b">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:42:11</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1281,17 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="b">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:42:13</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1302,17 @@
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="b">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:42:26</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1323,17 @@
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="b">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:42:28</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1344,17 @@
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="b">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:44:33</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1365,17 @@
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="b">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2025-09-18T12:45:51</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1386,17 @@
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="b">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2025-09-18T13:00:55</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1407,17 @@
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2025-09-18T13:00:58</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1428,17 @@
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="b">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2025-09-18T13:31:55</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1449,17 @@
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="b">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025-09-18T13:32:02</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1470,17 @@
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="b">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:02:57</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1491,17 @@
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="b">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:02:58</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1512,17 @@
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="b">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:03:06</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1533,17 @@
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="b">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:04:48</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1554,17 @@
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="b">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:04:53</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1575,17 @@
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="b">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:15:56</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1596,17 @@
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="b">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:16:21</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1617,17 @@
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
-      <c r="C57" t="b">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:16:23</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1638,17 @@
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="b">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:17:08</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1659,17 @@
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="b">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:17:12</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1680,17 @@
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="b">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:17:16</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1701,17 @@
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
-      <c r="C61" t="b">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:29:52</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1722,17 @@
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="b">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-09-18T14:29:54</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1743,17 @@
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="b">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:19:52</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1764,17 @@
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="b">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:19:53</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1785,17 @@
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="b">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:20:09</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1806,17 @@
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="b">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:20:10</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1827,17 @@
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
-      <c r="C67" t="b">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:20:41</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1848,17 @@
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="b">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:28:53</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1869,17 @@
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
-      <c r="C69" t="b">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:28:54</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1890,17 @@
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
-      <c r="C70" t="b">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:28:55</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1911,17 @@
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2025-09-19T03:28:59</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1932,17 @@
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
-      <c r="C72" t="b">
-        <v>1</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025-09-19T08:43:41</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1953,17 @@
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
-      <c r="C73" t="b">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2025-09-19T09:02:07</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1974,17 @@
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
-      <c r="C74" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2025-09-19T09:02:10</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1995,17 @@
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-09-19T09:02:26</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1641,12 +2016,17 @@
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="b">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2025-09-19T10:16:36</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1657,12 +2037,17 @@
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="b">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2025-09-19T10:16:38</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1673,12 +2058,17 @@
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="b">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2025-09-19T10:16:47</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1689,12 +2079,17 @@
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
-      <c r="C79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2025-09-19T14:46:37</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1705,12 +2100,17 @@
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-      <c r="C80" t="b">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2025-09-19T14:51:37</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1721,12 +2121,17 @@
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2025-09-19T14:51:39</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1737,12 +2142,17 @@
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="b">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2025-09-19T14:59:14</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1753,12 +2163,17 @@
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="b">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2025-09-19T14:59:17</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1769,12 +2184,17 @@
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
-      <c r="C84" t="b">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2025-09-19T15:36:20</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1785,12 +2205,17 @@
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="b">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2025-09-19T15:36:22</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1801,12 +2226,17 @@
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
-      <c r="C86" t="b">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2025-09-19T15:36:33</t>
+        </is>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1817,12 +2247,17 @@
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
-      <c r="C87" t="b">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-09-19T15:37:20</t>
+        </is>
+      </c>
+      <c r="D87" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1833,12 +2268,17 @@
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
-      <c r="C88" t="b">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2025-09-19T15:52:14</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1849,12 +2289,17 @@
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
-      <c r="C89" t="b">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2025-09-19T15:52:16</t>
+        </is>
+      </c>
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1865,12 +2310,17 @@
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
-      <c r="C90" t="b">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2025-09-19T16:16:53</t>
+        </is>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1881,12 +2331,17 @@
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
-      <c r="C91" t="b">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2025-09-19T16:17:17</t>
+        </is>
+      </c>
+      <c r="D91" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1897,12 +2352,17 @@
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
-      <c r="C92" t="b">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2025-09-19T16:17:49</t>
+        </is>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1913,12 +2373,17 @@
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="b">
-        <v>1</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2025-09-19T16:33:13</t>
+        </is>
+      </c>
+      <c r="D93" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1929,12 +2394,17 @@
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
-      <c r="C94" t="b">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2025-09-19T16:33:15</t>
+        </is>
+      </c>
+      <c r="D94" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -1945,12 +2415,17 @@
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="b">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2025-09-20T13:50:04</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>
@@ -1961,12 +2436,17 @@
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="b">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>no realtime audio sample; TouchEvent not supported</t>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2025-09-23T05:57:47</t>
+        </is>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
         </is>
       </c>
     </row>
@@ -1977,12 +2457,17 @@
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="b">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>no realtime audio sample; TouchEvent not supported</t>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2025-09-23T05:57:50</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
         </is>
       </c>
     </row>
@@ -1993,12 +2478,17 @@
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="b">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2025-09-23T08:14:45</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2499,17 @@
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
-      <c r="C99" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2025-09-23T08:15:41</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2520,17 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
-      <c r="C100" t="b">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:11:48</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2541,17 @@
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="b">
-        <v>1</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:12:28</t>
+        </is>
+      </c>
+      <c r="D101" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2562,17 @@
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="b">
-        <v>1</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:43</t>
+        </is>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2583,17 @@
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
-      <c r="C103" t="b">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:44</t>
+        </is>
+      </c>
+      <c r="D103" t="b">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2604,17 @@
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="b">
-        <v>1</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:44</t>
+        </is>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2625,17 @@
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
-      <c r="C105" t="b">
-        <v>1</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:45</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2646,17 @@
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="b">
-        <v>1</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:46</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2667,17 @@
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="b">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:48</t>
+        </is>
+      </c>
+      <c r="D107" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2688,17 @@
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="b">
-        <v>1</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:14:57</t>
+        </is>
+      </c>
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2169,12 +2709,17 @@
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="b">
-        <v>1</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:28:40</t>
+        </is>
+      </c>
+      <c r="D109" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2730,17 @@
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="b">
-        <v>1</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2025-09-23T09:28:44</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2751,17 @@
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
-      <c r="C111" t="b">
-        <v>1</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2025-09-23T10:51:46</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2772,17 @@
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="b">
-        <v>1</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2025-09-23T10:51:47</t>
+        </is>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2793,17 @@
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="b">
-        <v>1</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2025-09-23T10:51:51</t>
+        </is>
+      </c>
+      <c r="D113" t="b">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2814,17 @@
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="b">
-        <v>1</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2025-09-25T08:48:20</t>
+        </is>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2835,17 @@
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
-      <c r="C115" t="b">
-        <v>1</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>timezone info abnormal; no realtime audio sample</t>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2025-09-25T09:06:31</t>
+        </is>
+      </c>
+      <c r="D115" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2856,17 @@
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="b">
-        <v>1</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2025-09-25T11:34:28</t>
+        </is>
+      </c>
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2877,17 @@
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="b">
-        <v>1</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2025-09-25T11:34:31</t>
+        </is>
+      </c>
+      <c r="D117" t="b">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2898,17 @@
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="b">
-        <v>1</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2025-09-25T11:34:34</t>
+        </is>
+      </c>
+      <c r="D118" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2329,12 +2919,17 @@
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="b">
-        <v>1</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2025-09-25T11:48:20</t>
+        </is>
+      </c>
+      <c r="D119" t="b">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2940,17 @@
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="b">
-        <v>1</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2025-09-25T11:48:20</t>
+        </is>
+      </c>
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2961,17 @@
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="b">
-        <v>1</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2025-09-25T11:48:24</t>
+        </is>
+      </c>
+      <c r="D121" t="b">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2982,17 @@
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="b">
-        <v>1</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:10:02</t>
+        </is>
+      </c>
+      <c r="D122" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2393,12 +3003,17 @@
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="b">
-        <v>1</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:10:06</t>
+        </is>
+      </c>
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2409,12 +3024,17 @@
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
-      <c r="C124" t="b">
-        <v>1</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:40:12</t>
+        </is>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2425,12 +3045,17 @@
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
-      <c r="C125" t="b">
-        <v>1</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:40:15</t>
+        </is>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2441,12 +3066,17 @@
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="b">
-        <v>1</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:40:18</t>
+        </is>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2457,12 +3087,17 @@
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
-      <c r="C127" t="b">
-        <v>1</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:40:27</t>
+        </is>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2473,12 +3108,17 @@
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
-      <c r="C128" t="b">
-        <v>1</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>no realtime audio sample</t>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:40:31</t>
+        </is>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2489,12 +3129,1613 @@
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
-      <c r="C129" t="b">
-        <v>0</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>looks normal</t>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2025-09-25T12:40:36</t>
+        </is>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>m.ik.k.am.u.e.rtio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:13:02</t>
+        </is>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>m.ik.k.am.u.e.rtio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:13:28</t>
+        </is>
+      </c>
+      <c r="D131" t="b">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:13:31</t>
+        </is>
+      </c>
+      <c r="D132" t="b">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>m.ik.k.am.u.e.rtio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:14:24</t>
+        </is>
+      </c>
+      <c r="D133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:14:27</t>
+        </is>
+      </c>
+      <c r="D134" t="b">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>m.ik.k.am.u.e.rtio@gmail.com</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:14:46</t>
+        </is>
+      </c>
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2025-09-25T14:14:48</t>
+        </is>
+      </c>
+      <c r="D136" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2025-09-25T15:24:58</t>
+        </is>
+      </c>
+      <c r="D137" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2025-09-25T15:24:58</t>
+        </is>
+      </c>
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2025-09-25T15:25:01</t>
+        </is>
+      </c>
+      <c r="D139" t="b">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2025-09-27T10:54:12</t>
+        </is>
+      </c>
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2025-09-27T10:58:04</t>
+        </is>
+      </c>
+      <c r="D141" t="b">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2025-09-27T10:58:08</t>
+        </is>
+      </c>
+      <c r="D142" t="b">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2025-09-27T10:58:27</t>
+        </is>
+      </c>
+      <c r="D143" t="b">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:30:38</t>
+        </is>
+      </c>
+      <c r="D144" t="b">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>no fonts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:34:53</t>
+        </is>
+      </c>
+      <c r="D145" t="b">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:35:09</t>
+        </is>
+      </c>
+      <c r="D146" t="b">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:41:07</t>
+        </is>
+      </c>
+      <c r="D147" t="b">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:41:16</t>
+        </is>
+      </c>
+      <c r="D148" t="b">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>no fonts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:41:46</t>
+        </is>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>no fonts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:43:02</t>
+        </is>
+      </c>
+      <c r="D150" t="b">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>no fonts detected; TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:43:33</t>
+        </is>
+      </c>
+      <c r="D151" t="b">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>no fonts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:44:03</t>
+        </is>
+      </c>
+      <c r="D152" t="b">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>no fonts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2025-09-28T12:44:52</t>
+        </is>
+      </c>
+      <c r="D153" t="b">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>no fonts detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2025-09-28T13:18:04</t>
+        </is>
+      </c>
+      <c r="D154" t="b">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2025-09-29T08:50:35</t>
+        </is>
+      </c>
+      <c r="D155" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2025-09-29T08:56:54</t>
+        </is>
+      </c>
+      <c r="D156" t="b">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2025-09-29T13:39:59</t>
+        </is>
+      </c>
+      <c r="D157" t="b">
+        <v>1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2025-09-29T13:47:52</t>
+        </is>
+      </c>
+      <c r="D158" t="b">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2025-09-29T13:51:24</t>
+        </is>
+      </c>
+      <c r="D159" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2025-09-29T13:57:12</t>
+        </is>
+      </c>
+      <c r="D160" t="b">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>bot10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2025-10-07T06:29:55</t>
+        </is>
+      </c>
+      <c r="D161" t="b">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2025-10-07T11:34:55</t>
+        </is>
+      </c>
+      <c r="D162" t="b">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>bot10</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2025-10-08T12:19:51</t>
+        </is>
+      </c>
+      <c r="D163" t="b">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>bot10</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2025-10-08T12:26:51</t>
+        </is>
+      </c>
+      <c r="D164" t="b">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2025-10-08T12:26:54</t>
+        </is>
+      </c>
+      <c r="D165" t="b">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2025-10-08T19:24:50</t>
+        </is>
+      </c>
+      <c r="D166" t="b">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2025-10-09T03:26:43</t>
+        </is>
+      </c>
+      <c r="D167" t="b">
+        <v>1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2025-10-09T04:05:40</t>
+        </is>
+      </c>
+      <c r="D168" t="b">
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2025-10-09T04:06:20</t>
+        </is>
+      </c>
+      <c r="D169" t="b">
+        <v>1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2025-10-09T04:06:23</t>
+        </is>
+      </c>
+      <c r="D170" t="b">
+        <v>1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>bot11</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2025-10-09T07:12:25</t>
+        </is>
+      </c>
+      <c r="D171" t="b">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2025-10-09T07:12:36</t>
+        </is>
+      </c>
+      <c r="D172" t="b">
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:01:04</t>
+        </is>
+      </c>
+      <c r="D173" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:16:46</t>
+        </is>
+      </c>
+      <c r="D174" t="b">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:17:14</t>
+        </is>
+      </c>
+      <c r="D175" t="b">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:17:17</t>
+        </is>
+      </c>
+      <c r="D176" t="b">
+        <v>1</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:22:35</t>
+        </is>
+      </c>
+      <c r="D177" t="b">
+        <v>1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:22:38</t>
+        </is>
+      </c>
+      <c r="D178" t="b">
+        <v>1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:23:15</t>
+        </is>
+      </c>
+      <c r="D179" t="b">
+        <v>1</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:23:17</t>
+        </is>
+      </c>
+      <c r="D180" t="b">
+        <v>1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:23:30</t>
+        </is>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:23:34</t>
+        </is>
+      </c>
+      <c r="D182" t="b">
+        <v>1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:23:37</t>
+        </is>
+      </c>
+      <c r="D183" t="b">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:26:37</t>
+        </is>
+      </c>
+      <c r="D184" t="b">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:29:19</t>
+        </is>
+      </c>
+      <c r="D185" t="b">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-10-09T17:29:22</t>
+        </is>
+      </c>
+      <c r="D186" t="b">
+        <v>1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-10-10T14:27:20</t>
+        </is>
+      </c>
+      <c r="D187" t="b">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-10-10T14:27:27</t>
+        </is>
+      </c>
+      <c r="D188" t="b">
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-10-12T11:06:15</t>
+        </is>
+      </c>
+      <c r="D189" t="b">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-10-12T15:59:54</t>
+        </is>
+      </c>
+      <c r="D190" t="b">
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-10-12T16:14:57</t>
+        </is>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2025-10-12T16:15:01</t>
+        </is>
+      </c>
+      <c r="D192" t="b">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2025-10-13T05:53:01</t>
+        </is>
+      </c>
+      <c r="D193" t="b">
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2025-10-13T05:53:07</t>
+        </is>
+      </c>
+      <c r="D194" t="b">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-10-20T08:05:18</t>
+        </is>
+      </c>
+      <c r="D195" t="b">
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-10-20T08:05:25</t>
+        </is>
+      </c>
+      <c r="D196" t="b">
+        <v>0</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-10-20T08:38:05</t>
+        </is>
+      </c>
+      <c r="D197" t="b">
+        <v>0</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-10-20T08:38:10</t>
+        </is>
+      </c>
+      <c r="D198" t="b">
+        <v>0</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>bot15</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-10-20T10:53:22</t>
+        </is>
+      </c>
+      <c r="D199" t="b">
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-10-20T10:53:28</t>
+        </is>
+      </c>
+      <c r="D200" t="b">
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-10-20T10:53:34</t>
+        </is>
+      </c>
+      <c r="D201" t="b">
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2025-10-25T16:45:03</t>
+        </is>
+      </c>
+      <c r="D202" t="b">
+        <v>1</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2025-10-28T01:34:05</t>
+        </is>
+      </c>
+      <c r="D203" t="b">
+        <v>1</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2025-10-28T01:40:10</t>
+        </is>
+      </c>
+      <c r="D204" t="b">
+        <v>1</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2025-10-28T01:40:29</t>
+        </is>
+      </c>
+      <c r="D205" t="b">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>timezone info abnormal</t>
         </is>
       </c>
     </row>

--- a/data/level3_analysis.xlsx
+++ b/data/level3_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-09-13T12:25:40</t>
+          <t>2025-09-13 20:25:40</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -485,7 +485,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-09-13T12:25:42</t>
+          <t>2025-09-13 20:25:42</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -506,7 +506,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-09-13T13:23:37</t>
+          <t>2025-09-13 21:23:37</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -527,7 +527,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-09-13T13:24:09</t>
+          <t>2025-09-13 21:24:09</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -548,7 +548,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-09-13T13:24:14</t>
+          <t>2025-09-13 21:24:14</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -569,7 +569,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-09-13T13:24:23</t>
+          <t>2025-09-13 21:24:23</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -590,7 +590,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-09-13T13:24:25</t>
+          <t>2025-09-13 21:24:25</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -611,7 +611,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-09-13T13:37:24</t>
+          <t>2025-09-13 21:37:24</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -632,7 +632,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-09-13T13:40:59</t>
+          <t>2025-09-13 21:40:59</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -653,7 +653,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-09-13T13:42:38</t>
+          <t>2025-09-13 21:42:38</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -674,7 +674,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-13T13:42:41</t>
+          <t>2025-09-13 21:42:41</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -695,7 +695,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-09-13T13:43:43</t>
+          <t>2025-09-13 21:43:43</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -716,7 +716,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-09-13T13:43:46</t>
+          <t>2025-09-13 21:43:46</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -737,7 +737,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-09-13T13:54:44</t>
+          <t>2025-09-13 21:54:44</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -758,7 +758,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-09-13T13:54:52</t>
+          <t>2025-09-13 21:54:52</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -779,7 +779,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-09-15T11:58:03</t>
+          <t>2025-09-15 19:58:03</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -800,7 +800,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-09-15T11:58:18</t>
+          <t>2025-09-15 19:58:18</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -821,7 +821,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-09-15T13:03:46</t>
+          <t>2025-09-15 21:03:46</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -842,7 +842,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-09-15T14:03:26</t>
+          <t>2025-09-15 22:03:26</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -863,7 +863,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-09-15T17:11:02</t>
+          <t>2025-09-16 01:11:02</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -884,7 +884,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-09-15T17:11:05</t>
+          <t>2025-09-16 01:11:05</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -905,7 +905,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-09-15T17:11:45</t>
+          <t>2025-09-16 01:11:45</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -926,7 +926,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-09-15T17:11:47</t>
+          <t>2025-09-16 01:11:47</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -947,7 +947,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-09-16T13:25:10</t>
+          <t>2025-09-16 21:25:10</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -968,7 +968,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-09-16T15:41:16</t>
+          <t>2025-09-16 23:41:16</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -989,7 +989,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-09-16T15:41:22</t>
+          <t>2025-09-16 23:41:22</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -1010,7 +1010,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-09-17T06:57:11</t>
+          <t>2025-09-17 14:57:11</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -1031,7 +1031,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-09-17T06:57:11</t>
+          <t>2025-09-17 14:57:11</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -1052,7 +1052,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-09-17T06:57:14</t>
+          <t>2025-09-17 14:57:14</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -1073,7 +1073,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-09-17T07:04:37</t>
+          <t>2025-09-17 15:04:37</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -1094,7 +1094,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-09-17T07:04:39</t>
+          <t>2025-09-17 15:04:39</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -1115,7 +1115,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-09-18T08:13:30</t>
+          <t>2025-09-18 16:13:30</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -1136,7 +1136,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025-09-18T08:13:30</t>
+          <t>2025-09-18 16:13:30</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -1157,7 +1157,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-09-18T08:13:33</t>
+          <t>2025-09-18 16:13:33</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -1178,7 +1178,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-09-18T08:13:34</t>
+          <t>2025-09-18 16:13:34</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -1199,7 +1199,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-09-18T08:13:34</t>
+          <t>2025-09-18 16:13:34</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -1220,7 +1220,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-09-18T12:42:01</t>
+          <t>2025-09-18 20:42:01</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -1241,7 +1241,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-09-18T12:42:04</t>
+          <t>2025-09-18 20:42:04</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -1262,7 +1262,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-09-18T12:42:11</t>
+          <t>2025-09-18 20:42:11</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -1283,7 +1283,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025-09-18T12:42:13</t>
+          <t>2025-09-18 20:42:13</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -1304,7 +1304,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-09-18T12:42:26</t>
+          <t>2025-09-18 20:42:26</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -1325,7 +1325,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-09-18T12:42:28</t>
+          <t>2025-09-18 20:42:28</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -1346,7 +1346,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-09-18T12:44:33</t>
+          <t>2025-09-18 20:44:33</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -1367,7 +1367,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025-09-18T12:45:51</t>
+          <t>2025-09-18 20:45:51</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -1388,7 +1388,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2025-09-18T13:00:55</t>
+          <t>2025-09-18 21:00:55</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -1409,7 +1409,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2025-09-18T13:00:58</t>
+          <t>2025-09-18 21:00:58</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -1430,7 +1430,7 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2025-09-18T13:31:55</t>
+          <t>2025-09-18 21:31:55</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -1451,7 +1451,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025-09-18T13:32:02</t>
+          <t>2025-09-18 21:32:02</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -1472,7 +1472,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025-09-18T14:02:57</t>
+          <t>2025-09-18 22:02:57</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -1493,7 +1493,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-09-18T14:02:58</t>
+          <t>2025-09-18 22:02:58</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -1514,7 +1514,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025-09-18T14:03:06</t>
+          <t>2025-09-18 22:03:06</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -1535,7 +1535,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025-09-18T14:04:48</t>
+          <t>2025-09-18 22:04:48</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -1556,7 +1556,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025-09-18T14:04:53</t>
+          <t>2025-09-18 22:04:53</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -1577,7 +1577,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-09-18T14:15:56</t>
+          <t>2025-09-18 22:15:56</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -1598,7 +1598,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-09-18T14:16:21</t>
+          <t>2025-09-18 22:16:21</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -1619,7 +1619,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-09-18T14:16:23</t>
+          <t>2025-09-18 22:16:23</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -1640,7 +1640,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-09-18T14:17:08</t>
+          <t>2025-09-18 22:17:08</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -1661,7 +1661,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-09-18T14:17:12</t>
+          <t>2025-09-18 22:17:12</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -1682,7 +1682,7 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-09-18T14:17:16</t>
+          <t>2025-09-18 22:17:16</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -1703,7 +1703,7 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-09-18T14:29:52</t>
+          <t>2025-09-18 22:29:52</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -1724,7 +1724,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2025-09-18T14:29:54</t>
+          <t>2025-09-18 22:29:54</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -1745,7 +1745,7 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-09-19T03:19:52</t>
+          <t>2025-09-19 11:19:52</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -1766,7 +1766,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2025-09-19T03:19:53</t>
+          <t>2025-09-19 11:19:53</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -1787,7 +1787,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025-09-19T03:20:09</t>
+          <t>2025-09-19 11:20:09</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -1808,7 +1808,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2025-09-19T03:20:10</t>
+          <t>2025-09-19 11:20:10</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -1829,7 +1829,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2025-09-19T03:20:41</t>
+          <t>2025-09-19 11:20:41</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -1850,7 +1850,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-09-19T03:28:53</t>
+          <t>2025-09-19 11:28:53</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -1871,7 +1871,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025-09-19T03:28:54</t>
+          <t>2025-09-19 11:28:54</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -1892,7 +1892,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2025-09-19T03:28:55</t>
+          <t>2025-09-19 11:28:55</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -1913,7 +1913,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025-09-19T03:28:59</t>
+          <t>2025-09-19 11:28:59</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -1934,7 +1934,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-09-19T08:43:41</t>
+          <t>2025-09-19 16:43:41</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -1955,7 +1955,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-09-19T09:02:07</t>
+          <t>2025-09-19 17:02:07</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -1976,7 +1976,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2025-09-19T09:02:10</t>
+          <t>2025-09-19 17:02:10</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -1997,7 +1997,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2025-09-19T09:02:26</t>
+          <t>2025-09-19 17:02:26</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -2018,7 +2018,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2025-09-19T10:16:36</t>
+          <t>2025-09-19 18:16:36</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -2039,7 +2039,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-09-19T10:16:38</t>
+          <t>2025-09-19 18:16:38</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -2060,7 +2060,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2025-09-19T10:16:47</t>
+          <t>2025-09-19 18:16:47</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -2081,7 +2081,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2025-09-19T14:46:37</t>
+          <t>2025-09-19 22:46:37</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -2102,7 +2102,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-09-19T14:51:37</t>
+          <t>2025-09-19 22:51:37</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -2123,7 +2123,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2025-09-19T14:51:39</t>
+          <t>2025-09-19 22:51:39</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -2144,7 +2144,7 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2025-09-19T14:59:14</t>
+          <t>2025-09-19 22:59:14</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -2165,7 +2165,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2025-09-19T14:59:17</t>
+          <t>2025-09-19 22:59:17</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -2186,7 +2186,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-09-19T15:36:20</t>
+          <t>2025-09-19 23:36:20</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -2207,7 +2207,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2025-09-19T15:36:22</t>
+          <t>2025-09-19 23:36:22</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -2228,7 +2228,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2025-09-19T15:36:33</t>
+          <t>2025-09-19 23:36:33</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -2249,7 +2249,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2025-09-19T15:37:20</t>
+          <t>2025-09-19 23:37:20</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -2270,7 +2270,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2025-09-19T15:52:14</t>
+          <t>2025-09-19 23:52:14</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -2291,7 +2291,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2025-09-19T15:52:16</t>
+          <t>2025-09-19 23:52:16</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -2312,7 +2312,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2025-09-19T16:16:53</t>
+          <t>2025-09-20 00:16:53</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -2333,7 +2333,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2025-09-19T16:17:17</t>
+          <t>2025-09-20 00:17:17</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -2354,7 +2354,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025-09-19T16:17:49</t>
+          <t>2025-09-20 00:17:49</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -2375,7 +2375,7 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2025-09-19T16:33:13</t>
+          <t>2025-09-20 00:33:13</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -2396,7 +2396,7 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025-09-19T16:33:15</t>
+          <t>2025-09-20 00:33:15</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -2417,7 +2417,7 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-09-20T13:50:04</t>
+          <t>2025-09-20 21:50:04</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -2438,7 +2438,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025-09-23T05:57:47</t>
+          <t>2025-09-23 13:57:47</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -2459,7 +2459,7 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-09-23T05:57:50</t>
+          <t>2025-09-23 13:57:50</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -2480,7 +2480,7 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-09-23T08:14:45</t>
+          <t>2025-09-23 16:14:45</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -2501,7 +2501,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-09-23T08:15:41</t>
+          <t>2025-09-23 16:15:41</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -2522,7 +2522,7 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-09-23T09:11:48</t>
+          <t>2025-09-23 17:11:48</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -2543,7 +2543,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-09-23T09:12:28</t>
+          <t>2025-09-23 17:12:28</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -2564,7 +2564,7 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:43</t>
+          <t>2025-09-23 17:14:43</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -2585,7 +2585,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:44</t>
+          <t>2025-09-23 17:14:44</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -2606,7 +2606,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:44</t>
+          <t>2025-09-23 17:14:44</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -2627,7 +2627,7 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:45</t>
+          <t>2025-09-23 17:14:45</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -2648,7 +2648,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:46</t>
+          <t>2025-09-23 17:14:46</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -2669,7 +2669,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:48</t>
+          <t>2025-09-23 17:14:48</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -2690,7 +2690,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-09-23T09:14:57</t>
+          <t>2025-09-23 17:14:57</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -2711,7 +2711,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-09-23T09:28:40</t>
+          <t>2025-09-23 17:28:40</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -2732,7 +2732,7 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-09-23T09:28:44</t>
+          <t>2025-09-23 17:28:44</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -2753,7 +2753,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2025-09-23T10:51:46</t>
+          <t>2025-09-23 18:51:46</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -2774,7 +2774,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-09-23T10:51:47</t>
+          <t>2025-09-23 18:51:47</t>
         </is>
       </c>
       <c r="D112" t="b">
@@ -2795,7 +2795,7 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2025-09-23T10:51:51</t>
+          <t>2025-09-23 18:51:51</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -2816,7 +2816,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2025-09-25T08:48:20</t>
+          <t>2025-09-25 16:48:20</t>
         </is>
       </c>
       <c r="D114" t="b">
@@ -2837,7 +2837,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2025-09-25T09:06:31</t>
+          <t>2025-09-25 17:06:31</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -2858,7 +2858,7 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2025-09-25T11:34:28</t>
+          <t>2025-09-25 19:34:28</t>
         </is>
       </c>
       <c r="D116" t="b">
@@ -2879,7 +2879,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2025-09-25T11:34:31</t>
+          <t>2025-09-25 19:34:31</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -2900,7 +2900,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2025-09-25T11:34:34</t>
+          <t>2025-09-25 19:34:34</t>
         </is>
       </c>
       <c r="D118" t="b">
@@ -2921,7 +2921,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2025-09-25T11:48:20</t>
+          <t>2025-09-25 19:48:20</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -2942,7 +2942,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2025-09-25T11:48:20</t>
+          <t>2025-09-25 19:48:20</t>
         </is>
       </c>
       <c r="D120" t="b">
@@ -2963,7 +2963,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2025-09-25T11:48:24</t>
+          <t>2025-09-25 19:48:24</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -2984,7 +2984,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2025-09-25T12:10:02</t>
+          <t>2025-09-25 20:10:02</t>
         </is>
       </c>
       <c r="D122" t="b">
@@ -3005,7 +3005,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2025-09-25T12:10:06</t>
+          <t>2025-09-25 20:10:06</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -3026,7 +3026,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2025-09-25T12:40:12</t>
+          <t>2025-09-25 20:40:12</t>
         </is>
       </c>
       <c r="D124" t="b">
@@ -3047,7 +3047,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2025-09-25T12:40:15</t>
+          <t>2025-09-25 20:40:15</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -3068,7 +3068,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2025-09-25T12:40:18</t>
+          <t>2025-09-25 20:40:18</t>
         </is>
       </c>
       <c r="D126" t="b">
@@ -3089,7 +3089,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2025-09-25T12:40:27</t>
+          <t>2025-09-25 20:40:27</t>
         </is>
       </c>
       <c r="D127" t="b">
@@ -3110,7 +3110,7 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2025-09-25T12:40:31</t>
+          <t>2025-09-25 20:40:31</t>
         </is>
       </c>
       <c r="D128" t="b">
@@ -3131,7 +3131,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2025-09-25T12:40:36</t>
+          <t>2025-09-25 20:40:36</t>
         </is>
       </c>
       <c r="D129" t="b">
@@ -3152,7 +3152,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2025-09-25T14:13:02</t>
+          <t>2025-09-25 22:13:02</t>
         </is>
       </c>
       <c r="D130" t="b">
@@ -3173,7 +3173,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2025-09-25T14:13:28</t>
+          <t>2025-09-25 22:13:28</t>
         </is>
       </c>
       <c r="D131" t="b">
@@ -3194,7 +3194,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2025-09-25T14:13:31</t>
+          <t>2025-09-25 22:13:31</t>
         </is>
       </c>
       <c r="D132" t="b">
@@ -3215,7 +3215,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2025-09-25T14:14:24</t>
+          <t>2025-09-25 22:14:24</t>
         </is>
       </c>
       <c r="D133" t="b">
@@ -3236,7 +3236,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2025-09-25T14:14:27</t>
+          <t>2025-09-25 22:14:27</t>
         </is>
       </c>
       <c r="D134" t="b">
@@ -3257,7 +3257,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2025-09-25T14:14:46</t>
+          <t>2025-09-25 22:14:46</t>
         </is>
       </c>
       <c r="D135" t="b">
@@ -3278,7 +3278,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2025-09-25T14:14:48</t>
+          <t>2025-09-25 22:14:48</t>
         </is>
       </c>
       <c r="D136" t="b">
@@ -3299,7 +3299,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2025-09-25T15:24:58</t>
+          <t>2025-09-25 23:24:58</t>
         </is>
       </c>
       <c r="D137" t="b">
@@ -3320,7 +3320,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2025-09-25T15:24:58</t>
+          <t>2025-09-25 23:24:58</t>
         </is>
       </c>
       <c r="D138" t="b">
@@ -3341,7 +3341,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2025-09-25T15:25:01</t>
+          <t>2025-09-25 23:25:01</t>
         </is>
       </c>
       <c r="D139" t="b">
@@ -3362,7 +3362,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2025-09-27T10:54:12</t>
+          <t>2025-09-27 18:54:12</t>
         </is>
       </c>
       <c r="D140" t="b">
@@ -3383,7 +3383,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2025-09-27T10:58:04</t>
+          <t>2025-09-27 18:58:04</t>
         </is>
       </c>
       <c r="D141" t="b">
@@ -3404,7 +3404,7 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2025-09-27T10:58:08</t>
+          <t>2025-09-27 18:58:08</t>
         </is>
       </c>
       <c r="D142" t="b">
@@ -3425,7 +3425,7 @@
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2025-09-27T10:58:27</t>
+          <t>2025-09-27 18:58:27</t>
         </is>
       </c>
       <c r="D143" t="b">
@@ -3446,7 +3446,7 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-09-28T12:30:38</t>
+          <t>2025-09-28 20:30:38</t>
         </is>
       </c>
       <c r="D144" t="b">
@@ -3467,7 +3467,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2025-09-28T12:34:53</t>
+          <t>2025-09-28 20:34:53</t>
         </is>
       </c>
       <c r="D145" t="b">
@@ -3488,7 +3488,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2025-09-28T12:35:09</t>
+          <t>2025-09-28 20:35:09</t>
         </is>
       </c>
       <c r="D146" t="b">
@@ -3509,7 +3509,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2025-09-28T12:41:07</t>
+          <t>2025-09-28 20:41:07</t>
         </is>
       </c>
       <c r="D147" t="b">
@@ -3530,7 +3530,7 @@
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2025-09-28T12:41:16</t>
+          <t>2025-09-28 20:41:16</t>
         </is>
       </c>
       <c r="D148" t="b">
@@ -3551,7 +3551,7 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2025-09-28T12:41:46</t>
+          <t>2025-09-28 20:41:46</t>
         </is>
       </c>
       <c r="D149" t="b">
@@ -3572,7 +3572,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2025-09-28T12:43:02</t>
+          <t>2025-09-28 20:43:02</t>
         </is>
       </c>
       <c r="D150" t="b">
@@ -3593,7 +3593,7 @@
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2025-09-28T12:43:33</t>
+          <t>2025-09-28 20:43:33</t>
         </is>
       </c>
       <c r="D151" t="b">
@@ -3614,7 +3614,7 @@
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2025-09-28T12:44:03</t>
+          <t>2025-09-28 20:44:03</t>
         </is>
       </c>
       <c r="D152" t="b">
@@ -3635,7 +3635,7 @@
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2025-09-28T12:44:52</t>
+          <t>2025-09-28 20:44:52</t>
         </is>
       </c>
       <c r="D153" t="b">
@@ -3656,7 +3656,7 @@
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2025-09-28T13:18:04</t>
+          <t>2025-09-28 21:18:04</t>
         </is>
       </c>
       <c r="D154" t="b">
@@ -3677,7 +3677,7 @@
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2025-09-29T08:50:35</t>
+          <t>2025-09-29 16:50:35</t>
         </is>
       </c>
       <c r="D155" t="b">
@@ -3698,7 +3698,7 @@
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2025-09-29T08:56:54</t>
+          <t>2025-09-29 16:56:54</t>
         </is>
       </c>
       <c r="D156" t="b">
@@ -3719,7 +3719,7 @@
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2025-09-29T13:39:59</t>
+          <t>2025-09-29 21:39:59</t>
         </is>
       </c>
       <c r="D157" t="b">
@@ -3740,7 +3740,7 @@
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2025-09-29T13:47:52</t>
+          <t>2025-09-29 21:47:52</t>
         </is>
       </c>
       <c r="D158" t="b">
@@ -3761,7 +3761,7 @@
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2025-09-29T13:51:24</t>
+          <t>2025-09-29 21:51:24</t>
         </is>
       </c>
       <c r="D159" t="b">
@@ -3782,7 +3782,7 @@
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2025-09-29T13:57:12</t>
+          <t>2025-09-29 21:57:12</t>
         </is>
       </c>
       <c r="D160" t="b">
@@ -3803,7 +3803,7 @@
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-10-07T06:29:55</t>
+          <t>2025-10-07 14:29:55</t>
         </is>
       </c>
       <c r="D161" t="b">
@@ -3824,7 +3824,7 @@
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2025-10-07T11:34:55</t>
+          <t>2025-10-07 19:34:55</t>
         </is>
       </c>
       <c r="D162" t="b">
@@ -3845,7 +3845,7 @@
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2025-10-08T12:19:51</t>
+          <t>2025-10-08 20:19:51</t>
         </is>
       </c>
       <c r="D163" t="b">
@@ -3866,7 +3866,7 @@
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2025-10-08T12:26:51</t>
+          <t>2025-10-08 20:26:51</t>
         </is>
       </c>
       <c r="D164" t="b">
@@ -3887,7 +3887,7 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2025-10-08T12:26:54</t>
+          <t>2025-10-08 20:26:54</t>
         </is>
       </c>
       <c r="D165" t="b">
@@ -3908,7 +3908,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2025-10-08T19:24:50</t>
+          <t>2025-10-09 03:24:50</t>
         </is>
       </c>
       <c r="D166" t="b">
@@ -3929,7 +3929,7 @@
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2025-10-09T03:26:43</t>
+          <t>2025-10-09 11:26:43</t>
         </is>
       </c>
       <c r="D167" t="b">
@@ -3950,7 +3950,7 @@
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2025-10-09T04:05:40</t>
+          <t>2025-10-09 12:05:40</t>
         </is>
       </c>
       <c r="D168" t="b">
@@ -3971,7 +3971,7 @@
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2025-10-09T04:06:20</t>
+          <t>2025-10-09 12:06:20</t>
         </is>
       </c>
       <c r="D169" t="b">
@@ -3992,7 +3992,7 @@
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2025-10-09T04:06:23</t>
+          <t>2025-10-09 12:06:23</t>
         </is>
       </c>
       <c r="D170" t="b">
@@ -4013,7 +4013,7 @@
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2025-10-09T07:12:25</t>
+          <t>2025-10-09 15:12:25</t>
         </is>
       </c>
       <c r="D171" t="b">
@@ -4034,7 +4034,7 @@
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2025-10-09T07:12:36</t>
+          <t>2025-10-09 15:12:36</t>
         </is>
       </c>
       <c r="D172" t="b">
@@ -4055,7 +4055,7 @@
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2025-10-09T17:01:04</t>
+          <t>2025-10-10 01:01:04</t>
         </is>
       </c>
       <c r="D173" t="b">
@@ -4076,7 +4076,7 @@
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2025-10-09T17:16:46</t>
+          <t>2025-10-10 01:16:46</t>
         </is>
       </c>
       <c r="D174" t="b">
@@ -4097,7 +4097,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2025-10-09T17:17:14</t>
+          <t>2025-10-10 01:17:14</t>
         </is>
       </c>
       <c r="D175" t="b">
@@ -4118,7 +4118,7 @@
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2025-10-09T17:17:17</t>
+          <t>2025-10-10 01:17:17</t>
         </is>
       </c>
       <c r="D176" t="b">
@@ -4139,7 +4139,7 @@
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2025-10-09T17:22:35</t>
+          <t>2025-10-10 01:22:35</t>
         </is>
       </c>
       <c r="D177" t="b">
@@ -4160,7 +4160,7 @@
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2025-10-09T17:22:38</t>
+          <t>2025-10-10 01:22:38</t>
         </is>
       </c>
       <c r="D178" t="b">
@@ -4181,7 +4181,7 @@
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2025-10-09T17:23:15</t>
+          <t>2025-10-10 01:23:15</t>
         </is>
       </c>
       <c r="D179" t="b">
@@ -4202,7 +4202,7 @@
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2025-10-09T17:23:17</t>
+          <t>2025-10-10 01:23:17</t>
         </is>
       </c>
       <c r="D180" t="b">
@@ -4223,7 +4223,7 @@
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2025-10-09T17:23:30</t>
+          <t>2025-10-10 01:23:30</t>
         </is>
       </c>
       <c r="D181" t="b">
@@ -4244,7 +4244,7 @@
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2025-10-09T17:23:34</t>
+          <t>2025-10-10 01:23:34</t>
         </is>
       </c>
       <c r="D182" t="b">
@@ -4265,7 +4265,7 @@
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2025-10-09T17:23:37</t>
+          <t>2025-10-10 01:23:37</t>
         </is>
       </c>
       <c r="D183" t="b">
@@ -4286,7 +4286,7 @@
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2025-10-09T17:26:37</t>
+          <t>2025-10-10 01:26:37</t>
         </is>
       </c>
       <c r="D184" t="b">
@@ -4307,7 +4307,7 @@
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2025-10-09T17:29:19</t>
+          <t>2025-10-10 01:29:19</t>
         </is>
       </c>
       <c r="D185" t="b">
@@ -4328,7 +4328,7 @@
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2025-10-09T17:29:22</t>
+          <t>2025-10-10 01:29:22</t>
         </is>
       </c>
       <c r="D186" t="b">
@@ -4349,7 +4349,7 @@
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2025-10-10T14:27:20</t>
+          <t>2025-10-10 22:27:20</t>
         </is>
       </c>
       <c r="D187" t="b">
@@ -4370,7 +4370,7 @@
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2025-10-10T14:27:27</t>
+          <t>2025-10-10 22:27:27</t>
         </is>
       </c>
       <c r="D188" t="b">
@@ -4391,7 +4391,7 @@
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2025-10-12T11:06:15</t>
+          <t>2025-10-12 19:06:15</t>
         </is>
       </c>
       <c r="D189" t="b">
@@ -4412,7 +4412,7 @@
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2025-10-12T15:59:54</t>
+          <t>2025-10-12 23:59:54</t>
         </is>
       </c>
       <c r="D190" t="b">
@@ -4433,7 +4433,7 @@
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2025-10-12T16:14:57</t>
+          <t>2025-10-13 00:14:57</t>
         </is>
       </c>
       <c r="D191" t="b">
@@ -4454,7 +4454,7 @@
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2025-10-12T16:15:01</t>
+          <t>2025-10-13 00:15:01</t>
         </is>
       </c>
       <c r="D192" t="b">
@@ -4475,7 +4475,7 @@
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2025-10-13T05:53:01</t>
+          <t>2025-10-13 13:53:01</t>
         </is>
       </c>
       <c r="D193" t="b">
@@ -4496,7 +4496,7 @@
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2025-10-13T05:53:07</t>
+          <t>2025-10-13 13:53:07</t>
         </is>
       </c>
       <c r="D194" t="b">
@@ -4517,7 +4517,7 @@
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2025-10-20T08:05:18</t>
+          <t>2025-10-20 16:05:18</t>
         </is>
       </c>
       <c r="D195" t="b">
@@ -4538,7 +4538,7 @@
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2025-10-20T08:05:25</t>
+          <t>2025-10-20 16:05:25</t>
         </is>
       </c>
       <c r="D196" t="b">
@@ -4559,7 +4559,7 @@
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2025-10-20T08:38:05</t>
+          <t>2025-10-20 16:38:05</t>
         </is>
       </c>
       <c r="D197" t="b">
@@ -4580,7 +4580,7 @@
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2025-10-20T08:38:10</t>
+          <t>2025-10-20 16:38:10</t>
         </is>
       </c>
       <c r="D198" t="b">
@@ -4601,7 +4601,7 @@
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2025-10-20T10:53:22</t>
+          <t>2025-10-20 18:53:22</t>
         </is>
       </c>
       <c r="D199" t="b">
@@ -4622,7 +4622,7 @@
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2025-10-20T10:53:28</t>
+          <t>2025-10-20 18:53:28</t>
         </is>
       </c>
       <c r="D200" t="b">
@@ -4643,7 +4643,7 @@
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025-10-20T10:53:34</t>
+          <t>2025-10-20 18:53:34</t>
         </is>
       </c>
       <c r="D201" t="b">
@@ -4664,7 +4664,7 @@
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2025-10-25T16:45:03</t>
+          <t>2025-10-26 00:45:03</t>
         </is>
       </c>
       <c r="D202" t="b">
@@ -4685,7 +4685,7 @@
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2025-10-28T01:34:05</t>
+          <t>2025-10-28 09:34:05</t>
         </is>
       </c>
       <c r="D203" t="b">
@@ -4706,7 +4706,7 @@
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2025-10-28T01:40:10</t>
+          <t>2025-10-28 09:40:10</t>
         </is>
       </c>
       <c r="D204" t="b">
@@ -4727,7 +4727,7 @@
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2025-10-28T01:40:29</t>
+          <t>2025-10-28 09:40:29</t>
         </is>
       </c>
       <c r="D205" t="b">
@@ -4736,6 +4736,6201 @@
       <c r="E205" t="inlineStr">
         <is>
           <t>timezone info abnormal</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2025-10-30 19:43:46</t>
+        </is>
+      </c>
+      <c r="D206" t="b">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2025-10-30 19:50:12</t>
+        </is>
+      </c>
+      <c r="D207" t="b">
+        <v>1</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2025-10-30 19:57:13</t>
+        </is>
+      </c>
+      <c r="D208" t="b">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2025-10-31 20:44:37</t>
+        </is>
+      </c>
+      <c r="D209" t="b">
+        <v>0</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2025-10-31 20:44:40</t>
+        </is>
+      </c>
+      <c r="D210" t="b">
+        <v>0</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2025-10-31 21:36:07</t>
+        </is>
+      </c>
+      <c r="D211" t="b">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2025-10-31 21:40:19</t>
+        </is>
+      </c>
+      <c r="D212" t="b">
+        <v>0</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2025-10-31 22:47:47</t>
+        </is>
+      </c>
+      <c r="D213" t="b">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2025-10-31 22:47:50</t>
+        </is>
+      </c>
+      <c r="D214" t="b">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2025-10-31 23:56:08</t>
+        </is>
+      </c>
+      <c r="D215" t="b">
+        <v>0</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2025-11-01 23:47:00</t>
+        </is>
+      </c>
+      <c r="D216" t="b">
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:21:14</t>
+        </is>
+      </c>
+      <c r="D217" t="b">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:42:53</t>
+        </is>
+      </c>
+      <c r="D218" t="b">
+        <v>1</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:07</t>
+        </is>
+      </c>
+      <c r="D219" t="b">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:10</t>
+        </is>
+      </c>
+      <c r="D220" t="b">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2025-11-03 15:39:08</t>
+        </is>
+      </c>
+      <c r="D221" t="b">
+        <v>0</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:20:26</t>
+        </is>
+      </c>
+      <c r="D222" t="b">
+        <v>1</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:20:31</t>
+        </is>
+      </c>
+      <c r="D223" t="b">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:20:37</t>
+        </is>
+      </c>
+      <c r="D224" t="b">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:20:42</t>
+        </is>
+      </c>
+      <c r="D225" t="b">
+        <v>1</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:20:48</t>
+        </is>
+      </c>
+      <c r="D226" t="b">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:20:54</t>
+        </is>
+      </c>
+      <c r="D227" t="b">
+        <v>1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:01</t>
+        </is>
+      </c>
+      <c r="D228" t="b">
+        <v>1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:08</t>
+        </is>
+      </c>
+      <c r="D229" t="b">
+        <v>1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:13</t>
+        </is>
+      </c>
+      <c r="D230" t="b">
+        <v>1</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:21</t>
+        </is>
+      </c>
+      <c r="D231" t="b">
+        <v>1</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:26</t>
+        </is>
+      </c>
+      <c r="D232" t="b">
+        <v>1</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:32</t>
+        </is>
+      </c>
+      <c r="D233" t="b">
+        <v>1</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:37</t>
+        </is>
+      </c>
+      <c r="D234" t="b">
+        <v>1</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:43</t>
+        </is>
+      </c>
+      <c r="D235" t="b">
+        <v>1</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:49</t>
+        </is>
+      </c>
+      <c r="D236" t="b">
+        <v>1</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:21:55</t>
+        </is>
+      </c>
+      <c r="D237" t="b">
+        <v>1</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:22:01</t>
+        </is>
+      </c>
+      <c r="D238" t="b">
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:22:06</t>
+        </is>
+      </c>
+      <c r="D239" t="b">
+        <v>1</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:22:12</t>
+        </is>
+      </c>
+      <c r="D240" t="b">
+        <v>1</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2025-11-03 19:22:18</t>
+        </is>
+      </c>
+      <c r="D241" t="b">
+        <v>1</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:28:12</t>
+        </is>
+      </c>
+      <c r="D242" t="b">
+        <v>1</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2025-11-03 20:29:59</t>
+        </is>
+      </c>
+      <c r="D243" t="b">
+        <v>1</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2025-11-04 15:37:53</t>
+        </is>
+      </c>
+      <c r="D244" t="b">
+        <v>0</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2025-11-07 21:03:33</t>
+        </is>
+      </c>
+      <c r="D245" t="b">
+        <v>1</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2025-11-07 21:03:57</t>
+        </is>
+      </c>
+      <c r="D246" t="b">
+        <v>1</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2025-11-07 21:05:23</t>
+        </is>
+      </c>
+      <c r="D247" t="b">
+        <v>0</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2025-11-08 02:01:05</t>
+        </is>
+      </c>
+      <c r="D248" t="b">
+        <v>1</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:42:22</t>
+        </is>
+      </c>
+      <c r="D249" t="b">
+        <v>1</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:42:28</t>
+        </is>
+      </c>
+      <c r="D250" t="b">
+        <v>1</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:15</t>
+        </is>
+      </c>
+      <c r="D251" t="b">
+        <v>1</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:20</t>
+        </is>
+      </c>
+      <c r="D252" t="b">
+        <v>1</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:26</t>
+        </is>
+      </c>
+      <c r="D253" t="b">
+        <v>1</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:31</t>
+        </is>
+      </c>
+      <c r="D254" t="b">
+        <v>1</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:37</t>
+        </is>
+      </c>
+      <c r="D255" t="b">
+        <v>1</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:43</t>
+        </is>
+      </c>
+      <c r="D256" t="b">
+        <v>1</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:49</t>
+        </is>
+      </c>
+      <c r="D257" t="b">
+        <v>1</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:51:55</t>
+        </is>
+      </c>
+      <c r="D258" t="b">
+        <v>1</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:01</t>
+        </is>
+      </c>
+      <c r="D259" t="b">
+        <v>1</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:07</t>
+        </is>
+      </c>
+      <c r="D260" t="b">
+        <v>1</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:13</t>
+        </is>
+      </c>
+      <c r="D261" t="b">
+        <v>1</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:19</t>
+        </is>
+      </c>
+      <c r="D262" t="b">
+        <v>1</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:27</t>
+        </is>
+      </c>
+      <c r="D263" t="b">
+        <v>1</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:32</t>
+        </is>
+      </c>
+      <c r="D264" t="b">
+        <v>1</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:38</t>
+        </is>
+      </c>
+      <c r="D265" t="b">
+        <v>1</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:45</t>
+        </is>
+      </c>
+      <c r="D266" t="b">
+        <v>1</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:51</t>
+        </is>
+      </c>
+      <c r="D267" t="b">
+        <v>1</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:52:58</t>
+        </is>
+      </c>
+      <c r="D268" t="b">
+        <v>1</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:53:03</t>
+        </is>
+      </c>
+      <c r="D269" t="b">
+        <v>1</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2025-11-08 15:53:09</t>
+        </is>
+      </c>
+      <c r="D270" t="b">
+        <v>1</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:02:41</t>
+        </is>
+      </c>
+      <c r="D271" t="b">
+        <v>0</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:02:44</t>
+        </is>
+      </c>
+      <c r="D272" t="b">
+        <v>0</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:27:48</t>
+        </is>
+      </c>
+      <c r="D273" t="b">
+        <v>1</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:27:51</t>
+        </is>
+      </c>
+      <c r="D274" t="b">
+        <v>1</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:30:01</t>
+        </is>
+      </c>
+      <c r="D275" t="b">
+        <v>1</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:10</t>
+        </is>
+      </c>
+      <c r="D276" t="b">
+        <v>1</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:12</t>
+        </is>
+      </c>
+      <c r="D277" t="b">
+        <v>1</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:16</t>
+        </is>
+      </c>
+      <c r="D278" t="b">
+        <v>1</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:19</t>
+        </is>
+      </c>
+      <c r="D279" t="b">
+        <v>1</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:22</t>
+        </is>
+      </c>
+      <c r="D280" t="b">
+        <v>1</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:25</t>
+        </is>
+      </c>
+      <c r="D281" t="b">
+        <v>1</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:29</t>
+        </is>
+      </c>
+      <c r="D282" t="b">
+        <v>1</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:31</t>
+        </is>
+      </c>
+      <c r="D283" t="b">
+        <v>1</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:36</t>
+        </is>
+      </c>
+      <c r="D284" t="b">
+        <v>1</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:38</t>
+        </is>
+      </c>
+      <c r="D285" t="b">
+        <v>1</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:42</t>
+        </is>
+      </c>
+      <c r="D286" t="b">
+        <v>1</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:45</t>
+        </is>
+      </c>
+      <c r="D287" t="b">
+        <v>1</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:48</t>
+        </is>
+      </c>
+      <c r="D288" t="b">
+        <v>1</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:51</t>
+        </is>
+      </c>
+      <c r="D289" t="b">
+        <v>1</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:55</t>
+        </is>
+      </c>
+      <c r="D290" t="b">
+        <v>1</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:48:58</t>
+        </is>
+      </c>
+      <c r="D291" t="b">
+        <v>1</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:02</t>
+        </is>
+      </c>
+      <c r="D292" t="b">
+        <v>1</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:05</t>
+        </is>
+      </c>
+      <c r="D293" t="b">
+        <v>1</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:08</t>
+        </is>
+      </c>
+      <c r="D294" t="b">
+        <v>1</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:11</t>
+        </is>
+      </c>
+      <c r="D295" t="b">
+        <v>1</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:14</t>
+        </is>
+      </c>
+      <c r="D296" t="b">
+        <v>1</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:17</t>
+        </is>
+      </c>
+      <c r="D297" t="b">
+        <v>1</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:21</t>
+        </is>
+      </c>
+      <c r="D298" t="b">
+        <v>1</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:24</t>
+        </is>
+      </c>
+      <c r="D299" t="b">
+        <v>1</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:28</t>
+        </is>
+      </c>
+      <c r="D300" t="b">
+        <v>1</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:30</t>
+        </is>
+      </c>
+      <c r="D301" t="b">
+        <v>1</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:34</t>
+        </is>
+      </c>
+      <c r="D302" t="b">
+        <v>1</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:37</t>
+        </is>
+      </c>
+      <c r="D303" t="b">
+        <v>1</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:41</t>
+        </is>
+      </c>
+      <c r="D304" t="b">
+        <v>1</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:43</t>
+        </is>
+      </c>
+      <c r="D305" t="b">
+        <v>1</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:46</t>
+        </is>
+      </c>
+      <c r="D306" t="b">
+        <v>1</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:49</t>
+        </is>
+      </c>
+      <c r="D307" t="b">
+        <v>1</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:54</t>
+        </is>
+      </c>
+      <c r="D308" t="b">
+        <v>1</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:49:56</t>
+        </is>
+      </c>
+      <c r="D309" t="b">
+        <v>1</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:50:00</t>
+        </is>
+      </c>
+      <c r="D310" t="b">
+        <v>1</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:50:03</t>
+        </is>
+      </c>
+      <c r="D311" t="b">
+        <v>1</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:50:07</t>
+        </is>
+      </c>
+      <c r="D312" t="b">
+        <v>1</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:50:09</t>
+        </is>
+      </c>
+      <c r="D313" t="b">
+        <v>1</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:50:13</t>
+        </is>
+      </c>
+      <c r="D314" t="b">
+        <v>1</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:50:15</t>
+        </is>
+      </c>
+      <c r="D315" t="b">
+        <v>1</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:58:25</t>
+        </is>
+      </c>
+      <c r="D316" t="b">
+        <v>1</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:58:30</t>
+        </is>
+      </c>
+      <c r="D317" t="b">
+        <v>1</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:58:36</t>
+        </is>
+      </c>
+      <c r="D318" t="b">
+        <v>1</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:58:42</t>
+        </is>
+      </c>
+      <c r="D319" t="b">
+        <v>1</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:58:48</t>
+        </is>
+      </c>
+      <c r="D320" t="b">
+        <v>1</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:58:55</t>
+        </is>
+      </c>
+      <c r="D321" t="b">
+        <v>1</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:00</t>
+        </is>
+      </c>
+      <c r="D322" t="b">
+        <v>1</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:06</t>
+        </is>
+      </c>
+      <c r="D323" t="b">
+        <v>1</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:12</t>
+        </is>
+      </c>
+      <c r="D324" t="b">
+        <v>1</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:18</t>
+        </is>
+      </c>
+      <c r="D325" t="b">
+        <v>1</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:24</t>
+        </is>
+      </c>
+      <c r="D326" t="b">
+        <v>1</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:29</t>
+        </is>
+      </c>
+      <c r="D327" t="b">
+        <v>1</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:36</t>
+        </is>
+      </c>
+      <c r="D328" t="b">
+        <v>1</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:42</t>
+        </is>
+      </c>
+      <c r="D329" t="b">
+        <v>1</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:48</t>
+        </is>
+      </c>
+      <c r="D330" t="b">
+        <v>1</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2025-11-08 16:59:53</t>
+        </is>
+      </c>
+      <c r="D331" t="b">
+        <v>1</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2025-11-08 17:00:00</t>
+        </is>
+      </c>
+      <c r="D332" t="b">
+        <v>1</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2025-11-08 17:00:06</t>
+        </is>
+      </c>
+      <c r="D333" t="b">
+        <v>1</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2025-11-08 17:00:13</t>
+        </is>
+      </c>
+      <c r="D334" t="b">
+        <v>1</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2025-11-08 17:00:18</t>
+        </is>
+      </c>
+      <c r="D335" t="b">
+        <v>1</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2025-11-12 15:52:48</t>
+        </is>
+      </c>
+      <c r="D336" t="b">
+        <v>0</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2025-11-14 20:09:11</t>
+        </is>
+      </c>
+      <c r="D337" t="b">
+        <v>0</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>bottest</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2025-11-25 20:49:51</t>
+        </is>
+      </c>
+      <c r="D338" t="b">
+        <v>1</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>bottest</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2025-11-25 20:49:53</t>
+        </is>
+      </c>
+      <c r="D339" t="b">
+        <v>1</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>bottest</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2025-11-25 20:49:54</t>
+        </is>
+      </c>
+      <c r="D340" t="b">
+        <v>1</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>bottest</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2025-11-25 20:49:54</t>
+        </is>
+      </c>
+      <c r="D341" t="b">
+        <v>1</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>bottest</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2025-11-25 20:49:56</t>
+        </is>
+      </c>
+      <c r="D342" t="b">
+        <v>1</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:07:17</t>
+        </is>
+      </c>
+      <c r="D343" t="b">
+        <v>0</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:07:40</t>
+        </is>
+      </c>
+      <c r="D344" t="b">
+        <v>0</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:07:42</t>
+        </is>
+      </c>
+      <c r="D345" t="b">
+        <v>0</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:19:18</t>
+        </is>
+      </c>
+      <c r="D346" t="b">
+        <v>1</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:19:21</t>
+        </is>
+      </c>
+      <c r="D347" t="b">
+        <v>1</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:22:12</t>
+        </is>
+      </c>
+      <c r="D348" t="b">
+        <v>0</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:22:15</t>
+        </is>
+      </c>
+      <c r="D349" t="b">
+        <v>0</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:33:30</t>
+        </is>
+      </c>
+      <c r="D350" t="b">
+        <v>1</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:33:33</t>
+        </is>
+      </c>
+      <c r="D351" t="b">
+        <v>1</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:50:04</t>
+        </is>
+      </c>
+      <c r="D352" t="b">
+        <v>0</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:50:07</t>
+        </is>
+      </c>
+      <c r="D353" t="b">
+        <v>0</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:53:03</t>
+        </is>
+      </c>
+      <c r="D354" t="b">
+        <v>0</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2025-11-26 22:53:05</t>
+        </is>
+      </c>
+      <c r="D355" t="b">
+        <v>0</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2025-11-26 23:02:36</t>
+        </is>
+      </c>
+      <c r="D356" t="b">
+        <v>0</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2025-11-26 23:02:39</t>
+        </is>
+      </c>
+      <c r="D357" t="b">
+        <v>0</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2025-11-26 23:54:44</t>
+        </is>
+      </c>
+      <c r="D358" t="b">
+        <v>0</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2025-11-26 23:54:47</t>
+        </is>
+      </c>
+      <c r="D359" t="b">
+        <v>0</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:02:07</t>
+        </is>
+      </c>
+      <c r="D360" t="b">
+        <v>0</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:02:10</t>
+        </is>
+      </c>
+      <c r="D361" t="b">
+        <v>0</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:10:34</t>
+        </is>
+      </c>
+      <c r="D362" t="b">
+        <v>1</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:10:37</t>
+        </is>
+      </c>
+      <c r="D363" t="b">
+        <v>1</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2025-11-27 02:10:46</t>
+        </is>
+      </c>
+      <c r="D364" t="b">
+        <v>1</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2025-11-27 02:10:49</t>
+        </is>
+      </c>
+      <c r="D365" t="b">
+        <v>1</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2025-11-27 02:16:34</t>
+        </is>
+      </c>
+      <c r="D366" t="b">
+        <v>1</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2025-11-27 02:16:37</t>
+        </is>
+      </c>
+      <c r="D367" t="b">
+        <v>1</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2025-12-01 19:03:53</t>
+        </is>
+      </c>
+      <c r="D368" t="b">
+        <v>1</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:09:06</t>
+        </is>
+      </c>
+      <c r="D369" t="b">
+        <v>1</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:19:27</t>
+        </is>
+      </c>
+      <c r="D370" t="b">
+        <v>0</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2025-12-02 19:06:19</t>
+        </is>
+      </c>
+      <c r="D371" t="b">
+        <v>0</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2025-12-02 19:06:42</t>
+        </is>
+      </c>
+      <c r="D372" t="b">
+        <v>1</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>03bot</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:52:38</t>
+        </is>
+      </c>
+      <c r="D373" t="b">
+        <v>1</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>03bot</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:13:41</t>
+        </is>
+      </c>
+      <c r="D374" t="b">
+        <v>1</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>bottest01</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:20:28</t>
+        </is>
+      </c>
+      <c r="D375" t="b">
+        <v>0</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>03bot</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:27:34</t>
+        </is>
+      </c>
+      <c r="D376" t="b">
+        <v>0</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>01bot</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:46:58</t>
+        </is>
+      </c>
+      <c r="D377" t="b">
+        <v>0</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>01bot</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:52:21</t>
+        </is>
+      </c>
+      <c r="D378" t="b">
+        <v>0</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>02bot</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2025-12-08 18:54:34</t>
+        </is>
+      </c>
+      <c r="D379" t="b">
+        <v>0</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>02bot</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2025-12-08 18:59:20</t>
+        </is>
+      </c>
+      <c r="D380" t="b">
+        <v>0</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2025-12-08 19:00:11</t>
+        </is>
+      </c>
+      <c r="D381" t="b">
+        <v>0</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2025-12-12 02:15:45</t>
+        </is>
+      </c>
+      <c r="D382" t="b">
+        <v>1</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2025-12-12 02:22:32</t>
+        </is>
+      </c>
+      <c r="D383" t="b">
+        <v>0</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>05bot</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2025-12-15 18:42:25</t>
+        </is>
+      </c>
+      <c r="D384" t="b">
+        <v>0</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>03bot</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2025-12-15 18:43:04</t>
+        </is>
+      </c>
+      <c r="D385" t="b">
+        <v>0</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2025-12-15 19:29:35</t>
+        </is>
+      </c>
+      <c r="D386" t="b">
+        <v>0</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2025-12-17 20:14:08</t>
+        </is>
+      </c>
+      <c r="D387" t="b">
+        <v>1</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:20:40</t>
+        </is>
+      </c>
+      <c r="D388" t="b">
+        <v>0</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:22:35</t>
+        </is>
+      </c>
+      <c r="D389" t="b">
+        <v>1</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:05:05</t>
+        </is>
+      </c>
+      <c r="D390" t="b">
+        <v>0</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:08:35</t>
+        </is>
+      </c>
+      <c r="D391" t="b">
+        <v>1</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:26:00</t>
+        </is>
+      </c>
+      <c r="D392" t="b">
+        <v>0</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:26:54</t>
+        </is>
+      </c>
+      <c r="D393" t="b">
+        <v>1</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2025-12-18 18:36:36</t>
+        </is>
+      </c>
+      <c r="D394" t="b">
+        <v>0</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2025-12-18 18:51:39</t>
+        </is>
+      </c>
+      <c r="D395" t="b">
+        <v>0</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2025-12-18 18:54:46</t>
+        </is>
+      </c>
+      <c r="D396" t="b">
+        <v>0</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:40:25</t>
+        </is>
+      </c>
+      <c r="D397" t="b">
+        <v>0</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2025-12-20 20:33:18</t>
+        </is>
+      </c>
+      <c r="D398" t="b">
+        <v>0</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2025-12-22 15:01:25</t>
+        </is>
+      </c>
+      <c r="D399" t="b">
+        <v>1</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2025-12-24 20:47:38</t>
+        </is>
+      </c>
+      <c r="D400" t="b">
+        <v>1</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2025-12-24 21:01:43</t>
+        </is>
+      </c>
+      <c r="D401" t="b">
+        <v>0</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2025-12-24 21:04:01</t>
+        </is>
+      </c>
+      <c r="D402" t="b">
+        <v>0</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2025-12-24 21:14:20</t>
+        </is>
+      </c>
+      <c r="D403" t="b">
+        <v>1</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:09:28</t>
+        </is>
+      </c>
+      <c r="D404" t="b">
+        <v>0</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:17:05</t>
+        </is>
+      </c>
+      <c r="D405" t="b">
+        <v>0</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:44:26</t>
+        </is>
+      </c>
+      <c r="D406" t="b">
+        <v>1</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>bot10</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2025-12-25 00:07:04</t>
+        </is>
+      </c>
+      <c r="D407" t="b">
+        <v>0</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2025-12-25 01:24:46</t>
+        </is>
+      </c>
+      <c r="D408" t="b">
+        <v>0</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2025-12-25 01:26:44</t>
+        </is>
+      </c>
+      <c r="D409" t="b">
+        <v>0</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2025-12-25 01:32:06</t>
+        </is>
+      </c>
+      <c r="D410" t="b">
+        <v>0</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2025-12-25 01:33:33</t>
+        </is>
+      </c>
+      <c r="D411" t="b">
+        <v>0</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2025-12-25 02:11:17</t>
+        </is>
+      </c>
+      <c r="D412" t="b">
+        <v>0</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2025-12-25 03:25:40</t>
+        </is>
+      </c>
+      <c r="D413" t="b">
+        <v>0</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>bot11</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2025-12-25 15:50:23</t>
+        </is>
+      </c>
+      <c r="D414" t="b">
+        <v>0</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>bot11</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2025-12-25 16:34:00</t>
+        </is>
+      </c>
+      <c r="D415" t="b">
+        <v>0</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2025-12-29 17:41:43</t>
+        </is>
+      </c>
+      <c r="D416" t="b">
+        <v>0</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2025-12-29 17:48:31</t>
+        </is>
+      </c>
+      <c r="D417" t="b">
+        <v>0</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2025-12-29 17:51:20</t>
+        </is>
+      </c>
+      <c r="D418" t="b">
+        <v>0</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2025-12-29 17:56:19</t>
+        </is>
+      </c>
+      <c r="D419" t="b">
+        <v>0</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:20:04</t>
+        </is>
+      </c>
+      <c r="D420" t="b">
+        <v>1</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:23:51</t>
+        </is>
+      </c>
+      <c r="D421" t="b">
+        <v>0</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:26:38</t>
+        </is>
+      </c>
+      <c r="D422" t="b">
+        <v>0</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:41:05</t>
+        </is>
+      </c>
+      <c r="D423" t="b">
+        <v>0</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:41:51</t>
+        </is>
+      </c>
+      <c r="D424" t="b">
+        <v>0</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:47:39</t>
+        </is>
+      </c>
+      <c r="D425" t="b">
+        <v>0</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:49:16</t>
+        </is>
+      </c>
+      <c r="D426" t="b">
+        <v>0</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2025-12-29 18:58:30</t>
+        </is>
+      </c>
+      <c r="D427" t="b">
+        <v>0</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:02:24</t>
+        </is>
+      </c>
+      <c r="D428" t="b">
+        <v>0</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>bot06</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2025-12-29 19:03:12</t>
+        </is>
+      </c>
+      <c r="D429" t="b">
+        <v>1</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2025-12-31 01:43:24</t>
+        </is>
+      </c>
+      <c r="D430" t="b">
+        <v>1</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:19:11</t>
+        </is>
+      </c>
+      <c r="D431" t="b">
+        <v>0</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:22:12</t>
+        </is>
+      </c>
+      <c r="D432" t="b">
+        <v>1</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:29:46</t>
+        </is>
+      </c>
+      <c r="D433" t="b">
+        <v>1</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:36:51</t>
+        </is>
+      </c>
+      <c r="D434" t="b">
+        <v>0</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-01-01 17:49:08</t>
+        </is>
+      </c>
+      <c r="D435" t="b">
+        <v>0</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-01-05 18:34:24</t>
+        </is>
+      </c>
+      <c r="D436" t="b">
+        <v>1</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>bot10</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-01-05 18:42:50</t>
+        </is>
+      </c>
+      <c r="D437" t="b">
+        <v>0</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-01-08 19:25:03</t>
+        </is>
+      </c>
+      <c r="D438" t="b">
+        <v>0</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-01-13 16:51:22</t>
+        </is>
+      </c>
+      <c r="D439" t="b">
+        <v>0</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:39:08</t>
+        </is>
+      </c>
+      <c r="D440" t="b">
+        <v>1</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:40:04</t>
+        </is>
+      </c>
+      <c r="D441" t="b">
+        <v>1</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:40:42</t>
+        </is>
+      </c>
+      <c r="D442" t="b">
+        <v>1</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:42:42</t>
+        </is>
+      </c>
+      <c r="D443" t="b">
+        <v>1</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-01-15 16:11:23</t>
+        </is>
+      </c>
+      <c r="D444" t="b">
+        <v>1</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-01-22 14:25:55</t>
+        </is>
+      </c>
+      <c r="D445" t="b">
+        <v>0</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>bot09</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-01-23 16:37:01</t>
+        </is>
+      </c>
+      <c r="D446" t="b">
+        <v>0</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-01-23 17:33:23</t>
+        </is>
+      </c>
+      <c r="D447" t="b">
+        <v>0</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-01-23 17:35:33</t>
+        </is>
+      </c>
+      <c r="D448" t="b">
+        <v>0</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-01-25 20:46:39</t>
+        </is>
+      </c>
+      <c r="D449" t="b">
+        <v>1</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:07:03</t>
+        </is>
+      </c>
+      <c r="D450" t="b">
+        <v>0</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:08:31</t>
+        </is>
+      </c>
+      <c r="D451" t="b">
+        <v>0</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:37:36</t>
+        </is>
+      </c>
+      <c r="D452" t="b">
+        <v>0</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-02-09 20:26:31</t>
+        </is>
+      </c>
+      <c r="D453" t="b">
+        <v>1</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-02-09 20:27:01</t>
+        </is>
+      </c>
+      <c r="D454" t="b">
+        <v>0</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>bot01</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:36:06</t>
+        </is>
+      </c>
+      <c r="D455" t="b">
+        <v>1</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>bot01</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:36:07</t>
+        </is>
+      </c>
+      <c r="D456" t="b">
+        <v>1</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>bot01</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-02-23 20:21:58</t>
+        </is>
+      </c>
+      <c r="D457" t="b">
+        <v>1</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>bot01</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-02-23 20:46:43</t>
+        </is>
+      </c>
+      <c r="D458" t="b">
+        <v>1</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>timezone info abnormal; virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-02-23 21:08:19</t>
+        </is>
+      </c>
+      <c r="D459" t="b">
+        <v>1</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:15:19</t>
+        </is>
+      </c>
+      <c r="D460" t="b">
+        <v>0</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:17:12</t>
+        </is>
+      </c>
+      <c r="D461" t="b">
+        <v>0</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:43:53</t>
+        </is>
+      </c>
+      <c r="D462" t="b">
+        <v>0</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:32:05</t>
+        </is>
+      </c>
+      <c r="D463" t="b">
+        <v>0</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:47:07</t>
+        </is>
+      </c>
+      <c r="D464" t="b">
+        <v>1</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:49:56</t>
+        </is>
+      </c>
+      <c r="D465" t="b">
+        <v>0</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:51:22</t>
+        </is>
+      </c>
+      <c r="D466" t="b">
+        <v>0</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-02-25 20:03:21</t>
+        </is>
+      </c>
+      <c r="D467" t="b">
+        <v>0</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-02-25 20:04:52</t>
+        </is>
+      </c>
+      <c r="D468" t="b">
+        <v>0</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>bot02</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-02-25 21:30:25</t>
+        </is>
+      </c>
+      <c r="D469" t="b">
+        <v>0</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-02-25 21:41:02</t>
+        </is>
+      </c>
+      <c r="D470" t="b">
+        <v>0</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-02-25 23:02:33</t>
+        </is>
+      </c>
+      <c r="D471" t="b">
+        <v>0</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-02-25 23:06:07</t>
+        </is>
+      </c>
+      <c r="D472" t="b">
+        <v>0</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-02-26 14:44:31</t>
+        </is>
+      </c>
+      <c r="D473" t="b">
+        <v>0</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-02-26 14:44:53</t>
+        </is>
+      </c>
+      <c r="D474" t="b">
+        <v>0</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-02-26 18:38:23</t>
+        </is>
+      </c>
+      <c r="D475" t="b">
+        <v>0</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:03:39</t>
+        </is>
+      </c>
+      <c r="D476" t="b">
+        <v>0</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:33:56</t>
+        </is>
+      </c>
+      <c r="D477" t="b">
+        <v>0</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:40:48</t>
+        </is>
+      </c>
+      <c r="D478" t="b">
+        <v>0</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-02-26 19:41:29</t>
+        </is>
+      </c>
+      <c r="D479" t="b">
+        <v>0</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:51:28</t>
+        </is>
+      </c>
+      <c r="D480" t="b">
+        <v>1</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:52:58</t>
+        </is>
+      </c>
+      <c r="D481" t="b">
+        <v>1</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:08:00</t>
+        </is>
+      </c>
+      <c r="D482" t="b">
+        <v>1</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>bot06</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:30:40</t>
+        </is>
+      </c>
+      <c r="D483" t="b">
+        <v>1</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:57:54</t>
+        </is>
+      </c>
+      <c r="D484" t="b">
+        <v>1</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:29:41</t>
+        </is>
+      </c>
+      <c r="D485" t="b">
+        <v>0</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:44:02</t>
+        </is>
+      </c>
+      <c r="D486" t="b">
+        <v>0</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-03-03 20:12:09</t>
+        </is>
+      </c>
+      <c r="D487" t="b">
+        <v>0</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:46:05</t>
+        </is>
+      </c>
+      <c r="D488" t="b">
+        <v>1</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-03-06 01:52:08</t>
+        </is>
+      </c>
+      <c r="D489" t="b">
+        <v>1</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>TouchEvent not supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:03:35</t>
+        </is>
+      </c>
+      <c r="D490" t="b">
+        <v>0</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-03-06 15:29:12</t>
+        </is>
+      </c>
+      <c r="D491" t="b">
+        <v>0</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-03-06 16:42:58</t>
+        </is>
+      </c>
+      <c r="D492" t="b">
+        <v>0</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-03-06 16:47:55</t>
+        </is>
+      </c>
+      <c r="D493" t="b">
+        <v>0</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-03-06 16:51:02</t>
+        </is>
+      </c>
+      <c r="D494" t="b">
+        <v>0</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>bot03</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-03-06 19:16:51</t>
+        </is>
+      </c>
+      <c r="D495" t="b">
+        <v>0</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-03-06 19:48:46</t>
+        </is>
+      </c>
+      <c r="D496" t="b">
+        <v>0</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-03-06 21:07:41</t>
+        </is>
+      </c>
+      <c r="D497" t="b">
+        <v>1</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>speech synthesis missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-03-06 21:20:30</t>
+        </is>
+      </c>
+      <c r="D498" t="b">
+        <v>0</v>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-03-06 21:29:51</t>
+        </is>
+      </c>
+      <c r="D499" t="b">
+        <v>0</v>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:40:42</t>
+        </is>
+      </c>
+      <c r="D500" t="b">
+        <v>0</v>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>looks normal</t>
         </is>
       </c>
     </row>

--- a/data/level3_analysis.xlsx
+++ b/data/level3_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:E552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -930,11 +930,11 @@
         </is>
       </c>
       <c r="D24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="D96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -2463,11 +2463,11 @@
         </is>
       </c>
       <c r="D97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>no fonts detected; TouchEvent not supported</t>
+          <t>no fonts detected</t>
         </is>
       </c>
     </row>
@@ -3681,11 +3681,11 @@
         </is>
       </c>
       <c r="D155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3702,11 +3702,11 @@
         </is>
       </c>
       <c r="D156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3723,11 +3723,11 @@
         </is>
       </c>
       <c r="D157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3744,11 @@
         </is>
       </c>
       <c r="D158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3765,11 +3765,11 @@
         </is>
       </c>
       <c r="D159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3786,11 +3786,11 @@
         </is>
       </c>
       <c r="D160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="D166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3933,11 +3933,11 @@
         </is>
       </c>
       <c r="D167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="D169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -3996,11 +3996,11 @@
         </is>
       </c>
       <c r="D170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4059,11 +4059,11 @@
         </is>
       </c>
       <c r="D173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4080,11 +4080,11 @@
         </is>
       </c>
       <c r="D174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4101,11 +4101,11 @@
         </is>
       </c>
       <c r="D175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4122,11 +4122,11 @@
         </is>
       </c>
       <c r="D176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4143,11 +4143,11 @@
         </is>
       </c>
       <c r="D177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4164,11 +4164,11 @@
         </is>
       </c>
       <c r="D178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="D179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4206,11 +4206,11 @@
         </is>
       </c>
       <c r="D180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="D181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="D182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4269,11 +4269,11 @@
         </is>
       </c>
       <c r="D183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="D184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4311,11 +4311,11 @@
         </is>
       </c>
       <c r="D185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4332,11 +4332,11 @@
         </is>
       </c>
       <c r="D186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4668,11 +4668,11 @@
         </is>
       </c>
       <c r="D202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="D211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4899,11 @@
         </is>
       </c>
       <c r="D213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -4920,11 +4920,11 @@
         </is>
       </c>
       <c r="D214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>looks normal</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7482,11 +7482,11 @@
         </is>
       </c>
       <c r="D336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7503,11 +7503,11 @@
         </is>
       </c>
       <c r="D337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+          <t>no fonts detected; media devices missing; speech synthesis missing; timezone info abnormal; no offline audio sample; requestIdleCallback not supported; queueMicrotask not supported</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+          <t>no fonts detected; media devices missing; speech synthesis missing; timezone info abnormal; no offline audio sample; requestIdleCallback not supported; queueMicrotask not supported</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="D376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8343,11 +8343,11 @@
         </is>
       </c>
       <c r="D377" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8364,11 +8364,11 @@
         </is>
       </c>
       <c r="D378" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="D379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8406,11 +8406,11 @@
         </is>
       </c>
       <c r="D380" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8490,11 +8490,11 @@
         </is>
       </c>
       <c r="D384" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8511,11 +8511,11 @@
         </is>
       </c>
       <c r="D385" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+          <t>no fonts detected; media devices missing; speech synthesis missing; timezone info abnormal; no offline audio sample; requestIdleCallback not supported; queueMicrotask not supported</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+          <t>no fonts detected; media devices missing; speech synthesis missing; timezone info abnormal; no offline audio sample; requestIdleCallback not supported; queueMicrotask not supported</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -8973,11 +8973,11 @@
         </is>
       </c>
       <c r="D407" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9120,11 +9120,11 @@
         </is>
       </c>
       <c r="D414" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9141,11 +9141,11 @@
         </is>
       </c>
       <c r="D415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>no fonts detected; timezone info abnormal; no offline audio sample; DevTools artifacts present</t>
+          <t>no fonts detected; media devices missing; speech synthesis missing; timezone info abnormal; no offline audio sample; requestIdleCallback not supported; queueMicrotask not supported</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9603,11 +9603,11 @@
         </is>
       </c>
       <c r="D437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9645,11 +9645,11 @@
         </is>
       </c>
       <c r="D439" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9792,11 +9792,11 @@
         </is>
       </c>
       <c r="D446" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="D454" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10422,11 +10422,11 @@
         </is>
       </c>
       <c r="D476" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10443,11 +10443,11 @@
         </is>
       </c>
       <c r="D477" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10464,11 +10464,11 @@
         </is>
       </c>
       <c r="D478" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="D479" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10611,11 +10611,11 @@
         </is>
       </c>
       <c r="D485" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10632,11 +10632,11 @@
         </is>
       </c>
       <c r="D486" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10653,11 +10653,11 @@
         </is>
       </c>
       <c r="D487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.)</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>TouchEvent not supported</t>
+          <t>realtime audio blocked: blocked_by_autoplay_policy</t>
         </is>
       </c>
     </row>
@@ -10716,11 +10716,11 @@
         </is>
       </c>
       <c r="D490" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10737,11 +10737,11 @@
         </is>
       </c>
       <c r="D491" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10842,11 +10842,11 @@
         </is>
       </c>
       <c r="D496" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10884,11 +10884,11 @@
         </is>
       </c>
       <c r="D498" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10905,11 +10905,11 @@
         </is>
       </c>
       <c r="D499" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -10926,11 +10926,1103 @@
         </is>
       </c>
       <c r="D500" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-03-09 19:04:49</t>
+        </is>
+      </c>
+      <c r="D501" t="b">
+        <v>1</v>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:00:32</t>
+        </is>
+      </c>
+      <c r="D502" t="b">
+        <v>1</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:03:13</t>
+        </is>
+      </c>
+      <c r="D503" t="b">
+        <v>1</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:04:08</t>
+        </is>
+      </c>
+      <c r="D504" t="b">
+        <v>1</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:04:48</t>
+        </is>
+      </c>
+      <c r="D505" t="b">
+        <v>1</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:09:38</t>
+        </is>
+      </c>
+      <c r="D506" t="b">
+        <v>1</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:11:12</t>
+        </is>
+      </c>
+      <c r="D507" t="b">
+        <v>1</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:19:56</t>
+        </is>
+      </c>
+      <c r="D508" t="b">
+        <v>1</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:21:24</t>
+        </is>
+      </c>
+      <c r="D509" t="b">
+        <v>1</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:29:16</t>
+        </is>
+      </c>
+      <c r="D510" t="b">
+        <v>1</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr"/>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-03-09 21:35:42</t>
+        </is>
+      </c>
+      <c r="D511" t="b">
+        <v>1</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:32:26</t>
+        </is>
+      </c>
+      <c r="D512" t="b">
+        <v>1</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:33:36</t>
+        </is>
+      </c>
+      <c r="D513" t="b">
+        <v>1</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:34:02</t>
+        </is>
+      </c>
+      <c r="D514" t="b">
+        <v>1</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:34:09</t>
+        </is>
+      </c>
+      <c r="D515" t="b">
+        <v>1</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-03-10 18:34:16</t>
+        </is>
+      </c>
+      <c r="D516" t="b">
+        <v>1</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:01:44</t>
+        </is>
+      </c>
+      <c r="D517" t="b">
+        <v>0</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>looks normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:18:22</t>
+        </is>
+      </c>
+      <c r="D518" t="b">
+        <v>1</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:22:33</t>
+        </is>
+      </c>
+      <c r="D519" t="b">
+        <v>1</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:23:41</t>
+        </is>
+      </c>
+      <c r="D520" t="b">
+        <v>1</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:26:01</t>
+        </is>
+      </c>
+      <c r="D521" t="b">
+        <v>1</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:26:24</t>
+        </is>
+      </c>
+      <c r="D522" t="b">
+        <v>1</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-03-10 20:26:31</t>
+        </is>
+      </c>
+      <c r="D523" t="b">
+        <v>1</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-03-13 19:34:06</t>
+        </is>
+      </c>
+      <c r="D524" t="b">
+        <v>1</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: blocked_by_autoplay_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:41:08</t>
+        </is>
+      </c>
+      <c r="D525" t="b">
+        <v>1</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:25:13</t>
+        </is>
+      </c>
+      <c r="D526" t="b">
+        <v>1</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:31:31</t>
+        </is>
+      </c>
+      <c r="D527" t="b">
+        <v>1</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:39:44</t>
+        </is>
+      </c>
+      <c r="D528" t="b">
+        <v>1</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:44:23</t>
+        </is>
+      </c>
+      <c r="D529" t="b">
+        <v>1</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:47:56</t>
+        </is>
+      </c>
+      <c r="D530" t="b">
+        <v>1</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:04:13</t>
+        </is>
+      </c>
+      <c r="D531" t="b">
+        <v>1</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:04:46</t>
+        </is>
+      </c>
+      <c r="D532" t="b">
+        <v>1</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:06:40</t>
+        </is>
+      </c>
+      <c r="D533" t="b">
+        <v>1</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:15:57</t>
+        </is>
+      </c>
+      <c r="D534" t="b">
+        <v>1</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:09:26</t>
+        </is>
+      </c>
+      <c r="D535" t="b">
+        <v>1</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:35:41</t>
+        </is>
+      </c>
+      <c r="D536" t="b">
+        <v>1</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:39:33</t>
+        </is>
+      </c>
+      <c r="D537" t="b">
+        <v>1</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:41:33</t>
+        </is>
+      </c>
+      <c r="D538" t="b">
+        <v>1</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:45:44</t>
+        </is>
+      </c>
+      <c r="D539" t="b">
+        <v>1</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:51:42</t>
+        </is>
+      </c>
+      <c r="D540" t="b">
+        <v>1</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:54:00</t>
+        </is>
+      </c>
+      <c r="D541" t="b">
+        <v>1</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:58:56</t>
+        </is>
+      </c>
+      <c r="D542" t="b">
+        <v>1</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:59:16</t>
+        </is>
+      </c>
+      <c r="D543" t="b">
+        <v>1</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:00:14</t>
+        </is>
+      </c>
+      <c r="D544" t="b">
+        <v>1</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:02:13</t>
+        </is>
+      </c>
+      <c r="D545" t="b">
+        <v>1</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:02:35</t>
+        </is>
+      </c>
+      <c r="D546" t="b">
+        <v>1</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:08:00</t>
+        </is>
+      </c>
+      <c r="D547" t="b">
+        <v>1</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>bot13</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:10:18</t>
+        </is>
+      </c>
+      <c r="D548" t="b">
+        <v>1</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:19:31</t>
+        </is>
+      </c>
+      <c r="D549" t="b">
+        <v>1</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:28:10</t>
+        </is>
+      </c>
+      <c r="D550" t="b">
+        <v>1</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:32:59</t>
+        </is>
+      </c>
+      <c r="D551" t="b">
+        <v>1</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:34:59</t>
+        </is>
+      </c>
+      <c r="D552" t="b">
+        <v>1</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>

--- a/data/level3_analysis.xlsx
+++ b/data/level3_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E552"/>
+  <dimension ref="A1:E560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="D336" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="D337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="D376" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="D377" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="D378" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="D379" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="D380" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="D384" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="D385" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="D407" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="D414" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="D415" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="D437" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="D446" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="D454" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="D476" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         </is>
       </c>
       <c r="D477" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="D478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="D479" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="D485" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="D486" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="D487" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="D489" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="D490" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         </is>
       </c>
       <c r="D491" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         </is>
       </c>
       <c r="D496" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="D498" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="D499" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="D500" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="D501" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="D502" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         </is>
       </c>
       <c r="D503" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="D504" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="D505" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="D506" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="D507" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         </is>
       </c>
       <c r="D508" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="D509" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         </is>
       </c>
       <c r="D510" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         </is>
       </c>
       <c r="D511" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -11283,11 +11283,11 @@
         </is>
       </c>
       <c r="D517" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>looks normal</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>virtual GPU detected (SwiftShader/Google Inc.); realtime audio blocked: timeout</t>
+          <t>virtual GPU detected (SwiftShader/Google Inc.); touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>realtime audio blocked: blocked_by_autoplay_policy</t>
+          <t>realtime audio blocked: blocked_by_autoplay_policy; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,175 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>realtime audio blocked: timeout</t>
+          <t>touch support mismatch (level2=False, level3=True); realtime audio blocked: timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-03-17 17:27:59</t>
+        </is>
+      </c>
+      <c r="D553" t="b">
+        <v>1</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:05:44</t>
+        </is>
+      </c>
+      <c r="D554" t="b">
+        <v>1</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:12:04</t>
+        </is>
+      </c>
+      <c r="D555" t="b">
+        <v>1</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:25:34</t>
+        </is>
+      </c>
+      <c r="D556" t="b">
+        <v>1</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:26:47</t>
+        </is>
+      </c>
+      <c r="D557" t="b">
+        <v>1</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:47:34</t>
+        </is>
+      </c>
+      <c r="D558" t="b">
+        <v>1</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:49:12</t>
+        </is>
+      </c>
+      <c r="D559" t="b">
+        <v>1</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-03-17 18:51:08</t>
+        </is>
+      </c>
+      <c r="D560" t="b">
+        <v>1</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>touch support mismatch (level2=False, level3=True); webdriver patch pattern co-occurs with trust/context anomalies; realtime audio blocked: timeout; webdriver descriptor suggests anti-detection patch</t>
         </is>
       </c>
     </row>
